--- a/Scripts/Industry/Results_per_Country/2040_DK.xlsx
+++ b/Scripts/Industry/Results_per_Country/2040_DK.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,41 +452,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>109.8448100815261</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1593.263093362518</v>
       </c>
       <c r="D2" t="n">
-        <v>1981.417607785804</v>
+        <v>4523.401245616466</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+        <v>109.8448100815261</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1593.263093362518</v>
+      </c>
+      <c r="D3" t="n">
+        <v>221.8531386947635</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Methanol</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -496,37 +502,61 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Biomass</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>434.6639416952042</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Biogas</t>
+          <t>Biomass</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>416.0443856700241</v>
+        <v>434.6639416952042</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Biogas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
+        <v>416.0443856700241</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
         <v>1130.709280420575</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>2320.130499135898</v>
       </c>
     </row>
   </sheetData>
